--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/PARALAMA - 19_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/PARALAMA - 19_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PARALAMA DIANTEIRO PRETO WESTER TIAN FAN CG150 2004 A 2008</t>
+          <t>PARALAMA DIANTEIRO PRETO INJETADO WESTER TITAN FAN CG150 2004 A 2008</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -457,7 +457,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -520,7 +524,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PARALAMA DIANTEIRO PRTO PEÇA+ CG FAN TITAN150 2004 A 2008</t>
+          <t>PARALAMA DIANTEIRO PRETO PEÇA+ CG FAN TITAN150 2004 A 2008</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -528,7 +532,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -549,7 +557,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -557,7 +569,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7899101665347</t>
+          <t> </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -645,7 +657,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -691,7 +707,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -712,7 +732,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -733,7 +757,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -750,7 +778,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -796,7 +828,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -809,7 +845,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PARALAMA DIANTEIRO STYLU BRS TAMBOR</t>
+          <t>PARALAMA DIANTEIRO STYLU BROS TAMBOR</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -829,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7897845422669</t>
+          <t>7899101677265</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SUPORTE PARALAMA DIANTEIR XRE PARA BROS DISCO</t>
+          <t>PARALAMA TRASEIRO XRE300 2010 A 2012</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -842,20 +878,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>18</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>7899101677265</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PARALAMA TRASEIRO XRE300 2010 A 2012</t>
+          <t xml:space="preserve">PARALAMA TRASEIRO HONDA </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -865,7 +901,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -873,20 +909,24 @@
       <c r="A21" t="n">
         <v>19</v>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>7899988709745</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARALAMA TRASEIRO HONDA </t>
+          <t>PARALAMA TRASEIRO ADAPTAVEL WESTER FAN125 2009 A 2013 PRETO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -896,12 +936,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7899988709745</t>
+          <t>7898469156108</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PARALAMA TRASEIRO ADAPTAVEL WESTER FAN125 2009 A 2013 PRETO</t>
+          <t>PARALAMA TRASEIRO SPORTIVE TITAN160 2016 1033</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -909,7 +949,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -917,12 +961,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7898469156108</t>
+          <t>7898574850731</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PARALAMA TRASEIRO SPORTIVE TITAN160 2016 1033</t>
+          <t>PARALAMA TRASEIRO SPORTIVE POP110 2016 A 2023</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -930,7 +974,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -938,12 +986,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7898574850731</t>
+          <t>7899093609985</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PARALAMA TRASEIRO SPORTIVE POP110 2016 A 2023</t>
+          <t>PARALAMA TRASEIRO  ADAPTAVEL CG150 SPORT 172701</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -953,7 +1001,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -963,12 +1011,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7898443600566</t>
+          <t>7899101673793</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SUPORTE PLACA SPORTIVE XTZ250/ LANDER 2100008</t>
+          <t>PARALAMA TRASEIRO PROTORK CB300R 2010 A 2013</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -978,7 +1026,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -988,22 +1036,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7898940972982</t>
+          <t>7899093629709</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SUPORTE PLACA SPORTIVE BRS NXR 2009 A 2011 2100007</t>
+          <t>PARALAMA TRASEIRO MELC CG TITAN160 2016 A 2023</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -1013,83 +1061,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7899093609985</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>PARALAMA TRASEIRO  ADAPTAVEL CG150 SPORT 172701</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>7899101673793</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>PARALAMA TRASEIRO PROTORK CB300R 2010 A 2013</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>7899093629709</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>PARALAMA TRASEIRO MELC CG TITAN160 2016 A 2023</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/PARALAMA - 19_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/PARALAMA - 19_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -632,11 +592,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,11 +612,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -682,11 +632,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -707,11 +652,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -732,11 +672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -757,11 +692,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -778,11 +708,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -803,11 +728,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -828,11 +748,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -853,11 +768,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -878,11 +788,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -899,11 +804,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -924,11 +824,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -949,11 +844,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -974,11 +864,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -999,11 +884,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1024,11 +904,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1049,11 +924,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1066,7 +936,6 @@
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
